--- a/research/traditional_assets/database/data/bahrain/bahrain_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.201</v>
-      </c>
-      <c r="E2">
-        <v>0.25305</v>
+        <v>0.252</v>
       </c>
       <c r="G2">
-        <v>0.1099556119213697</v>
+        <v>0.1294277929155313</v>
       </c>
       <c r="H2">
-        <v>0.1099556119213697</v>
+        <v>0.1294277929155313</v>
       </c>
       <c r="I2">
-        <v>0.1083703233988586</v>
+        <v>0.1498637602179836</v>
       </c>
       <c r="J2">
-        <v>0.1083703233988586</v>
+        <v>0.1498637602179836</v>
       </c>
       <c r="K2">
-        <v>19.08</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>0.1209892200380469</v>
+        <v>0.1498637602179836</v>
       </c>
       <c r="M2">
-        <v>11.698</v>
+        <v>6.36</v>
       </c>
       <c r="N2">
-        <v>0.04347082868821999</v>
+        <v>0.07653429602888087</v>
       </c>
       <c r="O2">
-        <v>0.6131027253668764</v>
+        <v>0.5781818181818182</v>
       </c>
       <c r="P2">
-        <v>11.64</v>
+        <v>6.36</v>
       </c>
       <c r="Q2">
-        <v>0.04325529542920847</v>
+        <v>0.07653429602888087</v>
       </c>
       <c r="R2">
-        <v>0.6100628930817611</v>
+        <v>0.5781818181818182</v>
       </c>
       <c r="S2">
-        <v>0.05799999999999983</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.004958112497862868</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="V2">
-        <v>0.3827573392790784</v>
+        <v>0.1564380264741276</v>
       </c>
       <c r="W2">
-        <v>0.1107548300662812</v>
+        <v>0.1426718547341116</v>
       </c>
       <c r="X2">
-        <v>0.09263983848027882</v>
+        <v>0.1460326405904854</v>
       </c>
       <c r="Y2">
-        <v>0.01811499158600238</v>
+        <v>-0.003360785856373838</v>
       </c>
       <c r="Z2">
-        <v>1.680018749733668</v>
+        <v>1.1505603887452</v>
       </c>
       <c r="AA2">
-        <v>0.2015072429120402</v>
+        <v>0.1724273062152206</v>
       </c>
       <c r="AB2">
-        <v>0.09259088527302307</v>
+        <v>0.1459409651868201</v>
       </c>
       <c r="AC2">
-        <v>0.1089163576390172</v>
+        <v>0.0264863410284005</v>
       </c>
       <c r="AD2">
-        <v>0.843</v>
+        <v>0.384</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.843</v>
+        <v>0.384</v>
       </c>
       <c r="AG2">
-        <v>-102.157</v>
+        <v>-12.616</v>
       </c>
       <c r="AH2">
-        <v>0.003122881497204965</v>
+        <v>0.004599683771740693</v>
       </c>
       <c r="AI2">
-        <v>0.004421877540743693</v>
+        <v>0.004523820743603035</v>
       </c>
       <c r="AJ2">
-        <v>-0.6119274243304599</v>
+        <v>-0.1789909766755576</v>
       </c>
       <c r="AK2">
-        <v>-1.165603642047853</v>
+        <v>-0.1755049802459518</v>
       </c>
       <c r="AL2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.04675540765391015</v>
-      </c>
-      <c r="AO2">
-        <v>341.8</v>
+        <v>0.03254237288135593</v>
       </c>
       <c r="AP2">
-        <v>-5.665945646145313</v>
-      </c>
-      <c r="AQ2">
-        <v>341.8</v>
+        <v>-1.069152542372881</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bahrain Kuwait Insurance Company B.S.C. (BAX:BKIC)</t>
+          <t>Solidarity Bahrain B.S.C. (BAX:SOLID)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,249 +713,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.179</v>
-      </c>
-      <c r="E3">
-        <v>0.0471</v>
+        <v>0.252</v>
       </c>
       <c r="G3">
-        <v>0.07783882783882784</v>
+        <v>0.1294277929155313</v>
       </c>
       <c r="H3">
-        <v>0.07783882783882784</v>
+        <v>0.1294277929155313</v>
       </c>
       <c r="I3">
-        <v>0.07793040293040293</v>
+        <v>0.1498637602179836</v>
       </c>
       <c r="J3">
-        <v>0.07793040293040293</v>
+        <v>0.1498637602179836</v>
       </c>
       <c r="K3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>0.09615384615384615</v>
+        <v>0.1498637602179836</v>
       </c>
       <c r="M3">
-        <v>5.928</v>
+        <v>6.36</v>
       </c>
       <c r="N3">
-        <v>0.0347887323943662</v>
+        <v>0.07653429602888087</v>
       </c>
       <c r="O3">
-        <v>0.5645714285714286</v>
+        <v>0.5781818181818182</v>
       </c>
       <c r="P3">
-        <v>5.87</v>
+        <v>6.36</v>
       </c>
       <c r="Q3">
-        <v>0.03444835680751174</v>
+        <v>0.07653429602888087</v>
       </c>
       <c r="R3">
-        <v>0.559047619047619</v>
+        <v>0.5781818181818182</v>
       </c>
       <c r="S3">
-        <v>0.05799999999999983</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.009784075573549229</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>89.3</v>
+        <v>13</v>
       </c>
       <c r="V3">
-        <v>0.5240610328638498</v>
+        <v>0.1564380264741276</v>
       </c>
       <c r="W3">
-        <v>0.1036525172754195</v>
+        <v>0.1426718547341116</v>
       </c>
       <c r="X3">
-        <v>0.09258678644388033</v>
+        <v>0.1460326405904854</v>
       </c>
       <c r="Y3">
-        <v>0.01106573083153922</v>
+        <v>-0.003360785856373838</v>
       </c>
       <c r="Z3">
-        <v>3.384157679434734</v>
+        <v>1.1505603887452</v>
       </c>
       <c r="AA3">
-        <v>0.2637287715383662</v>
+        <v>0.1724273062152206</v>
       </c>
       <c r="AB3">
-        <v>0.09254810433283184</v>
+        <v>0.1459409651868201</v>
       </c>
       <c r="AC3">
-        <v>0.1711806672055343</v>
+        <v>0.0264863410284005</v>
       </c>
       <c r="AD3">
-        <v>0.448</v>
+        <v>0.384</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.448</v>
+        <v>0.384</v>
       </c>
       <c r="AG3">
-        <v>-88.852</v>
+        <v>-12.616</v>
       </c>
       <c r="AH3">
-        <v>0.002622213897733658</v>
+        <v>0.004599683771740693</v>
       </c>
       <c r="AI3">
-        <v>0.003959415986142044</v>
+        <v>0.004523820743603035</v>
       </c>
       <c r="AJ3">
-        <v>-1.089566880855447</v>
+        <v>-0.1789909766755576</v>
       </c>
       <c r="AK3">
-        <v>-3.725763166722577</v>
+        <v>-0.1755049802459518</v>
       </c>
       <c r="AL3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.05137614678899082</v>
-      </c>
-      <c r="AO3">
-        <v>170.2</v>
+        <v>0.03254237288135593</v>
       </c>
       <c r="AP3">
-        <v>-10.1894495412844</v>
-      </c>
-      <c r="AQ3">
-        <v>170.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Solidarity Bahrain B.S.C. (BAX:SOLID)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.223</v>
-      </c>
-      <c r="E4">
-        <v>0.459</v>
-      </c>
-      <c r="G4">
-        <v>0.1822680412371134</v>
-      </c>
-      <c r="H4">
-        <v>0.1822680412371134</v>
-      </c>
-      <c r="I4">
-        <v>0.1769072164948454</v>
-      </c>
-      <c r="J4">
-        <v>0.1769072164948454</v>
-      </c>
-      <c r="K4">
-        <v>8.58</v>
-      </c>
-      <c r="L4">
-        <v>0.1769072164948454</v>
-      </c>
-      <c r="M4">
-        <v>5.77</v>
-      </c>
-      <c r="N4">
-        <v>0.05845997973657548</v>
-      </c>
-      <c r="O4">
-        <v>0.6724941724941724</v>
-      </c>
-      <c r="P4">
-        <v>5.77</v>
-      </c>
-      <c r="Q4">
-        <v>0.05845997973657548</v>
-      </c>
-      <c r="R4">
-        <v>0.6724941724941724</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>13.7</v>
-      </c>
-      <c r="V4">
-        <v>0.1388044579533941</v>
-      </c>
-      <c r="W4">
-        <v>0.1178571428571429</v>
-      </c>
-      <c r="X4">
-        <v>0.0926928905166773</v>
-      </c>
-      <c r="Y4">
-        <v>0.02516425234046557</v>
-      </c>
-      <c r="Z4">
-        <v>0.7873376623376624</v>
-      </c>
-      <c r="AA4">
-        <v>0.1392857142857143</v>
-      </c>
-      <c r="AB4">
-        <v>0.09263366621321431</v>
-      </c>
-      <c r="AC4">
-        <v>0.04665204807249998</v>
-      </c>
-      <c r="AD4">
-        <v>0.395</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.395</v>
-      </c>
-      <c r="AG4">
-        <v>-13.305</v>
-      </c>
-      <c r="AH4">
-        <v>0.003986073969423281</v>
-      </c>
-      <c r="AI4">
-        <v>0.005097103038905737</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1558053750219568</v>
-      </c>
-      <c r="AK4">
-        <v>-0.2085586644721373</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0.04242749731471536</v>
-      </c>
-      <c r="AP4">
-        <v>-1.429108485499463</v>
+        <v>-1.069152542372881</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bahrain/bahrain_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_insurance_prop_cas.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.252</v>
+        <v>0.143</v>
+      </c>
+      <c r="E2">
+        <v>0.195</v>
       </c>
       <c r="G2">
-        <v>0.1294277929155313</v>
+        <v>0.1532066508313539</v>
       </c>
       <c r="H2">
-        <v>0.1294277929155313</v>
+        <v>0.1532066508313539</v>
       </c>
       <c r="I2">
-        <v>0.1498637602179836</v>
+        <v>0.160332541567696</v>
       </c>
       <c r="J2">
-        <v>0.1498637602179836</v>
+        <v>0.160332541567696</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="L2">
-        <v>0.1498637602179836</v>
+        <v>0.160332541567696</v>
       </c>
       <c r="M2">
-        <v>6.36</v>
+        <v>7.08</v>
       </c>
       <c r="N2">
-        <v>0.07653429602888087</v>
+        <v>0.0645985401459854</v>
       </c>
       <c r="O2">
-        <v>0.5781818181818182</v>
+        <v>0.5244444444444445</v>
       </c>
       <c r="P2">
-        <v>6.36</v>
+        <v>7.08</v>
       </c>
       <c r="Q2">
-        <v>0.07653429602888087</v>
+        <v>0.0645985401459854</v>
       </c>
       <c r="R2">
-        <v>0.5781818181818182</v>
+        <v>0.5244444444444445</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="V2">
-        <v>0.1564380264741276</v>
+        <v>0.1341240875912409</v>
       </c>
       <c r="W2">
-        <v>0.1426718547341116</v>
+        <v>0.1597633136094675</v>
       </c>
       <c r="X2">
-        <v>0.1460326405904854</v>
+        <v>0.1225588816332592</v>
       </c>
       <c r="Y2">
-        <v>-0.003360785856373838</v>
+        <v>0.03720443197620824</v>
       </c>
       <c r="Z2">
-        <v>1.1505603887452</v>
+        <v>1.28404550584073</v>
       </c>
       <c r="AA2">
-        <v>0.1724273062152206</v>
+        <v>0.205874279440022</v>
       </c>
       <c r="AB2">
-        <v>0.1459409651868201</v>
+        <v>0.1225302951469018</v>
       </c>
       <c r="AC2">
-        <v>0.0264863410284005</v>
+        <v>0.08334398429312019</v>
       </c>
       <c r="AD2">
-        <v>0.384</v>
+        <v>0.345</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.384</v>
+        <v>0.345</v>
       </c>
       <c r="AG2">
-        <v>-12.616</v>
+        <v>-14.355</v>
       </c>
       <c r="AH2">
-        <v>0.004599683771740693</v>
+        <v>0.003137932602664969</v>
       </c>
       <c r="AI2">
-        <v>0.004523820743603035</v>
+        <v>0.00383567735838568</v>
       </c>
       <c r="AJ2">
-        <v>-0.1789909766755576</v>
+        <v>-0.150716573048454</v>
       </c>
       <c r="AK2">
-        <v>-0.1755049802459518</v>
+        <v>-0.1907767958003854</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.03254237288135593</v>
+        <v>0.02429577464788732</v>
       </c>
       <c r="AP2">
-        <v>-1.069152542372881</v>
+        <v>-1.010915492957746</v>
       </c>
     </row>
     <row r="3">
@@ -713,43 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.252</v>
+        <v>0.143</v>
+      </c>
+      <c r="E3">
+        <v>0.195</v>
       </c>
       <c r="G3">
-        <v>0.1294277929155313</v>
+        <v>0.1532066508313539</v>
       </c>
       <c r="H3">
-        <v>0.1294277929155313</v>
+        <v>0.1532066508313539</v>
       </c>
       <c r="I3">
-        <v>0.1498637602179836</v>
+        <v>0.160332541567696</v>
       </c>
       <c r="J3">
-        <v>0.1498637602179836</v>
+        <v>0.160332541567696</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="L3">
-        <v>0.1498637602179836</v>
+        <v>0.160332541567696</v>
       </c>
       <c r="M3">
-        <v>6.36</v>
+        <v>7.08</v>
       </c>
       <c r="N3">
-        <v>0.07653429602888087</v>
+        <v>0.0645985401459854</v>
       </c>
       <c r="O3">
-        <v>0.5781818181818182</v>
+        <v>0.5244444444444445</v>
       </c>
       <c r="P3">
-        <v>6.36</v>
+        <v>7.08</v>
       </c>
       <c r="Q3">
-        <v>0.07653429602888087</v>
+        <v>0.0645985401459854</v>
       </c>
       <c r="R3">
-        <v>0.5781818181818182</v>
+        <v>0.5244444444444445</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="V3">
-        <v>0.1564380264741276</v>
+        <v>0.1341240875912409</v>
       </c>
       <c r="W3">
-        <v>0.1426718547341116</v>
+        <v>0.1597633136094675</v>
       </c>
       <c r="X3">
-        <v>0.1460326405904854</v>
+        <v>0.1225588816332592</v>
       </c>
       <c r="Y3">
-        <v>-0.003360785856373838</v>
+        <v>0.03720443197620824</v>
       </c>
       <c r="Z3">
-        <v>1.1505603887452</v>
+        <v>1.28404550584073</v>
       </c>
       <c r="AA3">
-        <v>0.1724273062152206</v>
+        <v>0.205874279440022</v>
       </c>
       <c r="AB3">
-        <v>0.1459409651868201</v>
+        <v>0.1225302951469018</v>
       </c>
       <c r="AC3">
-        <v>0.0264863410284005</v>
+        <v>0.08334398429312019</v>
       </c>
       <c r="AD3">
-        <v>0.384</v>
+        <v>0.345</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.384</v>
+        <v>0.345</v>
       </c>
       <c r="AG3">
-        <v>-12.616</v>
+        <v>-14.355</v>
       </c>
       <c r="AH3">
-        <v>0.004599683771740693</v>
+        <v>0.003137932602664969</v>
       </c>
       <c r="AI3">
-        <v>0.004523820743603035</v>
+        <v>0.00383567735838568</v>
       </c>
       <c r="AJ3">
-        <v>-0.1789909766755576</v>
+        <v>-0.150716573048454</v>
       </c>
       <c r="AK3">
-        <v>-0.1755049802459518</v>
+        <v>-0.1907767958003854</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.03254237288135593</v>
+        <v>0.02429577464788732</v>
       </c>
       <c r="AP3">
-        <v>-1.069152542372881</v>
+        <v>-1.010915492957746</v>
       </c>
     </row>
   </sheetData>
